--- a/03_Outputs/Agroindustrial_Occidente/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/Agroindustrial_Occidente/03_Ordenamiento/ordenamiento.xlsx
@@ -148,7 +148,7 @@
     <numFmt numFmtId="272" formatCode="#,##0.0"/>
     <numFmt numFmtId="273" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,23 +158,335 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -194,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -203,111 +515,167 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="167" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="169" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="170" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="171" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="172" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="173" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="174" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="174" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="175" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="176" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="176" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="177" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="178" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="178" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="179" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="180" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="182" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="190" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="196" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="197" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="199" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="200" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="200" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="201" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="202" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="202" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="203" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="205" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="206" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="206" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="207" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="208" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="208" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="209" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="210" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="210" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="211" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="212" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="213" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="215" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="216" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="216" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="217" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="218" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="218" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="219" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="220" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="220" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="221" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="222" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="222" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="223" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="224" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="224" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="225" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="226" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="226" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="227" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="228" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="228" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="229" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="230" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="230" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="231" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="232" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="233" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="234" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="234" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="235" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="236" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="236" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="237" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="239" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="240" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="241" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="242" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="242" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="243" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="244" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="244" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="245" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="246" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="247" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="248" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="248" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="249" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="250" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="250" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="251" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="252" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="253" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="254" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="254" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="255" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="256" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="256" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="257" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="258" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="258" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="259" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="260" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="260" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="261" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="262" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="262" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="263" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="264" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="16" numFmtId="264" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="265" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="266" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="266" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="267" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="268" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="268" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="269" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="270" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="270" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="271" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="272" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="272" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="19" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="273" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="12" fontId="20" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="13" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="14" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="15" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="16" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="17" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="18" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="19" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="20" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="21" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="22" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="31" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="23" fontId="31" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="32" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="24" fontId="32" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="33" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="25" fontId="33" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="34" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="26" fontId="34" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -636,12 +1004,12 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="93.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="94.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -928,34 +1296,34 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="137" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="137" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="137" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="137" t="inlineStr">
         <is>
           <t>Predios con uso adecuado del suelo rural</t>
         </is>
@@ -980,7 +1348,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="112">
+      <c r="E2" s="138">
         <v>0.580964565312986</v>
       </c>
     </row>
@@ -1003,7 +1371,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="112">
+      <c r="E3" s="138">
         <v>0.490477316590846</v>
       </c>
     </row>
@@ -1026,7 +1394,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="112" t="inlineStr">
+      <c r="E4" s="138" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1051,7 +1419,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="112" t="inlineStr">
+      <c r="E5" s="138" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1076,7 +1444,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="112">
+      <c r="E6" s="138">
         <v>0.464104800529024</v>
       </c>
     </row>
@@ -1099,7 +1467,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="112">
+      <c r="E7" s="138">
         <v>0.37682808037146</v>
       </c>
     </row>
@@ -1115,17 +1483,17 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="140" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="140" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1183,17 +1551,17 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="142" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1271,23 +1639,23 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="144" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="144" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="144" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1575,23 +1943,23 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="146" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="146" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="146" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1879,17 +2247,17 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="148" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1967,17 +2335,17 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="150" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="150" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2055,23 +2423,23 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="152" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="152" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="152" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2269,23 +2637,23 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="154" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="154" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="154" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2633,17 +3001,17 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="156" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="156" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2721,101 +3089,101 @@
   <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="76.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="77.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="48.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de energía (municipal)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de energía (agregado)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de acueducto (municipal)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de acueducto (agregado)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de alcantarillado (municipal)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de alcantarillado (agregado)</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de recolección de basuras (municipal)</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de recolección de basuras (agregado)</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de internet (municipal)</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de internet (agregado)</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de gas natural (municipal)</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de gas natural (agregado)</t>
         </is>
@@ -2840,50 +3208,50 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="11">
         <v>0.985480673934589</v>
       </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G2" s="12">
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" s="15">
         <v>0.870136082945795</v>
       </c>
-      <c r="H2" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" s="16">
+      <c r="H2" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" s="19">
         <v>0.770930853091408</v>
       </c>
-      <c r="J2" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" s="20">
+      <c r="J2" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" s="23">
         <v>0.607978196233895</v>
       </c>
-      <c r="L2" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" s="24">
+      <c r="L2" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" s="27">
         <v>0.284655409011207</v>
       </c>
-      <c r="N2" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" s="28">
+      <c r="N2" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" s="31">
         <v>0</v>
       </c>
-      <c r="P2" s="30" t="inlineStr">
+      <c r="P2" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2908,50 +3276,50 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="11">
         <v>0.983472679327051</v>
       </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G3" s="12">
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" s="15">
         <v>0.693658699325021</v>
       </c>
-      <c r="H3" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" s="16">
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" s="19">
         <v>0.461690341678313</v>
       </c>
-      <c r="J3" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" s="20">
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" s="23">
         <v>0.729325472863663</v>
       </c>
-      <c r="L3" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" s="24">
+      <c r="L3" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" s="27">
         <v>0.334220227278677</v>
       </c>
-      <c r="N3" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" s="28">
+      <c r="N3" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" s="31">
         <v>0.316411115331</v>
       </c>
-      <c r="P3" s="30" t="inlineStr">
+      <c r="P3" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2976,50 +3344,50 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="11">
         <v>0.861494883856183</v>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G4" s="12">
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" s="15">
         <v>0.580699072766055</v>
       </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" s="16">
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" s="19">
         <v>0.420974620027394</v>
       </c>
-      <c r="J4" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" s="20">
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" s="23">
         <v>0.371659182044839</v>
       </c>
-      <c r="L4" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" s="24">
+      <c r="L4" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" s="27">
         <v>0.213895766314576</v>
       </c>
-      <c r="N4" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" s="28">
+      <c r="N4" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" s="31">
         <v>0.24628984569783</v>
       </c>
-      <c r="P4" s="30" t="inlineStr">
+      <c r="P4" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3044,50 +3412,50 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="11">
         <v>1</v>
       </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" s="12">
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" s="15">
         <v>0.958588788549544</v>
       </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I5" s="16">
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" s="19">
         <v>0.695478427113675</v>
       </c>
-      <c r="J5" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K5" s="20">
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" s="23">
         <v>0.981525070834549</v>
       </c>
-      <c r="L5" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" s="24">
+      <c r="L5" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" s="27">
         <v>0.259579591080792</v>
       </c>
-      <c r="N5" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" s="28">
+      <c r="N5" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" s="31">
         <v>0.449529225159887</v>
       </c>
-      <c r="P5" s="30" t="inlineStr">
+      <c r="P5" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3112,50 +3480,50 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="11">
         <v>0.989753057476654</v>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" s="12">
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" s="15">
         <v>0.805876281274828</v>
       </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I6" s="16">
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" s="19">
         <v>0.584471339819482</v>
       </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K6" s="20">
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" s="23">
         <v>0.970923038851769</v>
       </c>
-      <c r="L6" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" s="24">
+      <c r="L6" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" s="27">
         <v>0.219609203037289</v>
       </c>
-      <c r="N6" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" s="28">
+      <c r="N6" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" s="31">
         <v>0</v>
       </c>
-      <c r="P6" s="30" t="inlineStr">
+      <c r="P6" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3180,262 +3548,262 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="11">
         <v>0.936912549815776</v>
       </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" s="12">
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" s="15">
         <v>0.466363385718225</v>
       </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I7" s="16">
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" s="19">
         <v>0.315938541744994</v>
       </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K7" s="20">
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" s="23">
         <v>0.70596786725819</v>
       </c>
-      <c r="L7" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M7" s="24">
+      <c r="L7" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" s="27">
         <v>0.20386244579793</v>
       </c>
-      <c r="N7" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O7" s="28">
+      <c r="N7" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" s="31">
         <v>0</v>
       </c>
-      <c r="P7" s="30" t="inlineStr">
+      <c r="P7" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE (promedio ponderado; sin ECV oficial)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F8" s="11">
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F8" s="14">
         <v>0.947749849036444</v>
       </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H8" s="15">
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H8" s="18">
         <v>0.728482702776411</v>
       </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J8" s="19">
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" s="22">
         <v>0.522949593395592</v>
       </c>
-      <c r="K8" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L8" s="23">
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" s="26">
         <v>0.708520694847475</v>
       </c>
-      <c r="M8" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N8" s="27">
+      <c r="M8" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" s="30">
         <v>0.25245818565628</v>
       </c>
-      <c r="O8" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P8" s="31">
+      <c r="O8" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" s="34">
         <v>0.258184944753881</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>SUBREGIÓN OCCIDENTE (ECV oficial)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F9" s="11">
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" s="14">
         <v>0.975014049622315</v>
       </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H9" s="15">
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H9" s="18">
         <v>0.820279523369767</v>
       </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J9" s="19">
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" s="22">
         <v>0.650641830743369</v>
       </c>
-      <c r="K9" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L9" s="23">
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" s="26">
         <v>0.801509906445029</v>
       </c>
-      <c r="M9" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N9" s="27">
+      <c r="M9" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" s="30">
         <v>0.320985901103542</v>
       </c>
-      <c r="O9" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P9" s="31">
+      <c r="O9" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" s="34">
         <v>0.309591764699951</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>DEPARTAMENTO (ANTIOQUIA) (ECV oficial)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F10" s="11">
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F10" s="14">
         <v>0.992586544500931</v>
       </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H10" s="15">
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H10" s="18">
         <v>0.93579635079431</v>
       </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J10" s="19">
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" s="22">
         <v>0.866893560801633</v>
       </c>
-      <c r="K10" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L10" s="23">
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" s="26">
         <v>0.944698426552535</v>
       </c>
-      <c r="M10" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N10" s="27">
+      <c r="M10" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" s="30">
         <v>0.601239746666835</v>
       </c>
-      <c r="O10" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P10" s="31">
+      <c r="O10" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" s="34">
         <v>0.66955125810138</v>
       </c>
     </row>
@@ -3451,17 +3819,17 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="158" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="158" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3539,17 +3907,17 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="160" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="160" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3667,17 +4035,17 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="162" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="162" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3755,17 +4123,17 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="164" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="164" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3778,7 +4146,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>282.151763448522</v>
+        <v>82.6505165657285</v>
       </c>
     </row>
     <row r="3">
@@ -3788,7 +4156,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>237.10407239819</v>
+        <v>71.1053652230123</v>
       </c>
     </row>
     <row r="4">
@@ -3798,7 +4166,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>160.190261206063</v>
+        <v>40.4708158658497</v>
       </c>
     </row>
     <row r="5">
@@ -3808,7 +4176,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>849.710717237579</v>
+        <v>214.574341078152</v>
       </c>
     </row>
     <row r="6">
@@ -3818,7 +4186,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>58.1872010931451</v>
+        <v>12.0701434752904</v>
       </c>
     </row>
     <row r="7">
@@ -3828,7 +4196,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>174.916163648558</v>
+        <v>51.9114688128773</v>
       </c>
     </row>
   </sheetData>
@@ -3843,17 +4211,17 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="166" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="166" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3866,7 +4234,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.702020202020202</v>
+        <v>0.65948275862069</v>
       </c>
     </row>
     <row r="3">
@@ -3876,7 +4244,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.54907306434024</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="4">
@@ -3886,7 +4254,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.644187216909914</v>
+        <v>0.525896414342629</v>
       </c>
     </row>
     <row r="5">
@@ -3896,7 +4264,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.897162928938125</v>
+        <v>0.883586561095656</v>
       </c>
     </row>
     <row r="6">
@@ -3906,7 +4274,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.232876712328767</v>
+        <v>0.0660377358490566</v>
       </c>
     </row>
     <row r="7">
@@ -3916,7 +4284,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.797546012269939</v>
+        <v>0.65374677002584</v>
       </c>
     </row>
   </sheetData>
@@ -3931,28 +4299,28 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="168" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="168" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="168" t="inlineStr">
         <is>
           <t>Déficit cuantitativo de vivienda</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="168" t="inlineStr">
         <is>
           <t>Déficit cualitativo de vivienda</t>
         </is>
@@ -4066,47 +4434,47 @@
   <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="82.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="83.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="36" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="36" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="36" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="36" t="inlineStr">
         <is>
           <t>Km de vía primaria por km² del municipio</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="36" t="inlineStr">
         <is>
           <t>Km de vía secundaria por km² del municipio</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="36" t="inlineStr">
         <is>
           <t>Km de vía terciaria por km² del municipio</t>
         </is>
@@ -4131,13 +4499,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="32">
+      <c r="E2" s="38">
         <v>0</v>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="40">
         <v>0.0830685803721113</v>
       </c>
-      <c r="G2" s="36">
+      <c r="G2" s="42">
         <v>0.186282870406432</v>
       </c>
     </row>
@@ -4160,13 +4528,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="38">
         <v>0.207452710405416</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="40">
         <v>0.088041211298062</v>
       </c>
-      <c r="G3" s="36">
+      <c r="G3" s="42">
         <v>0.439350380722076</v>
       </c>
     </row>
@@ -4189,13 +4557,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="38">
         <v>0.0567891173414711</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="40">
         <v>0.0034542709189454</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="42">
         <v>0.0760538569168226</v>
       </c>
     </row>
@@ -4218,13 +4586,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="38">
         <v>0.0035202305949292</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="40">
         <v>0.0500777932480289</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="42">
         <v>0.102649307071936</v>
       </c>
     </row>
@@ -4247,13 +4615,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="38">
         <v>0</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="40">
         <v>0.048662783922224</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="42">
         <v>0.243434025087072</v>
       </c>
     </row>
@@ -4276,44 +4644,44 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="38">
         <v>0.128641272467931</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="40">
         <v>0.170630317990188</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="42">
         <v>0.396765117728189</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE (por área del municipio)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" s="33">
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="39">
         <v>0.0480352652011083</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="41">
         <v>0.0423887279404246</v>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="43">
         <v>0.152603774198529</v>
       </c>
     </row>
@@ -4329,46 +4697,46 @@
   <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="73.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="5" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="74.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="5" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="45" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="45" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="45" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="45" t="inlineStr">
         <is>
           <t>Km de vía primaria por cada 1.000 hab.</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="45" t="inlineStr">
         <is>
           <t>Km de vía secundaria por cada 1.000 hab.</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="45" t="inlineStr">
         <is>
           <t>Km de vía terciaria por cada 1.000 hab.</t>
         </is>
@@ -4393,13 +4761,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="38">
+      <c r="E2" s="47">
         <v>0</v>
       </c>
-      <c r="F2" s="40">
+      <c r="F2" s="49">
         <v>8.68094588258817</v>
       </c>
-      <c r="G2" s="42">
+      <c r="G2" s="51">
         <v>19.4671861443576</v>
       </c>
     </row>
@@ -4422,13 +4790,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="47">
         <v>4.65584779766554</v>
       </c>
-      <c r="F3" s="40">
+      <c r="F3" s="49">
         <v>1.9759032259681</v>
       </c>
-      <c r="G3" s="42">
+      <c r="G3" s="51">
         <v>9.86031225377033</v>
       </c>
     </row>
@@ -4451,13 +4819,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="47">
         <v>4.55967598903667</v>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="49">
         <v>0.277348141793377</v>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="51">
         <v>6.10646830751188</v>
       </c>
     </row>
@@ -4480,13 +4848,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="47">
         <v>0.224165229119437</v>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="49">
         <v>3.18891041212201</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="51">
         <v>6.53661878624591</v>
       </c>
     </row>
@@ -4509,13 +4877,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="47">
         <v>0</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="49">
         <v>2.4604552206317</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="51">
         <v>12.3083487961183</v>
       </c>
     </row>
@@ -4538,44 +4906,44 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="47">
         <v>4.74406826562978</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="49">
         <v>6.2925518474902</v>
       </c>
-      <c r="G7" s="42">
+      <c r="G7" s="51">
         <v>14.6320132552513</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE (por población)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" s="39">
+      <c r="C8" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="48">
         <v>2.79002704927401</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="50">
         <v>2.45995580240848</v>
       </c>
-      <c r="G8" s="43">
+      <c r="G8" s="52">
         <v>8.85877015764573</v>
       </c>
     </row>
@@ -4591,71 +4959,71 @@
   <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="54.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="54" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="54" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral total ($)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral urbano ($)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral rural ($)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="54" t="inlineStr">
         <is>
           <t>Proporción del avalúo catastral urbano sobre el total</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="54" t="inlineStr">
         <is>
           <t>Proporción del avalúo catastral rural sobre el total</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Estado del catastro rural</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="54" t="inlineStr">
         <is>
           <t>Estado del catastro urbano</t>
         </is>
@@ -4680,19 +5048,19 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="44">
+      <c r="E2" s="56">
         <v>57819472000</v>
       </c>
-      <c r="F2" s="46">
+      <c r="F2" s="58">
         <v>22227246000</v>
       </c>
-      <c r="G2" s="48">
+      <c r="G2" s="60">
         <v>35592226000</v>
       </c>
-      <c r="H2" s="50">
+      <c r="H2" s="62">
         <v>0.384424921763381</v>
       </c>
-      <c r="I2" s="52">
+      <c r="I2" s="64">
         <v>0.615575078236619</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -4725,19 +5093,19 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="44">
+      <c r="E3" s="56">
         <v>248487534000</v>
       </c>
-      <c r="F3" s="46">
+      <c r="F3" s="58">
         <v>118377126000</v>
       </c>
-      <c r="G3" s="48">
+      <c r="G3" s="60">
         <v>130110408000</v>
       </c>
-      <c r="H3" s="50">
+      <c r="H3" s="62">
         <v>0.476390602355127</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3" s="64">
         <v>0.523609397644873</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -4770,19 +5138,19 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="56">
         <v>287227423000</v>
       </c>
-      <c r="F4" s="46">
+      <c r="F4" s="58">
         <v>110711211000</v>
       </c>
-      <c r="G4" s="48">
+      <c r="G4" s="60">
         <v>176516212000</v>
       </c>
-      <c r="H4" s="50">
+      <c r="H4" s="62">
         <v>0.385447913864408</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4" s="64">
         <v>0.614552086135592</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -4815,19 +5183,19 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="56">
         <v>428065872000</v>
       </c>
-      <c r="F5" s="46">
+      <c r="F5" s="58">
         <v>291026304000</v>
       </c>
-      <c r="G5" s="48">
+      <c r="G5" s="60">
         <v>137039568000</v>
       </c>
-      <c r="H5" s="50">
+      <c r="H5" s="62">
         <v>0.679863364580487</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="64">
         <v>0.320136635419513</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -4860,19 +5228,19 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="56">
         <v>78537344000</v>
       </c>
-      <c r="F6" s="46">
+      <c r="F6" s="58">
         <v>45425754000</v>
       </c>
-      <c r="G6" s="48">
+      <c r="G6" s="60">
         <v>33111590000</v>
       </c>
-      <c r="H6" s="50">
+      <c r="H6" s="62">
         <v>0.578396870665756</v>
       </c>
-      <c r="I6" s="52">
+      <c r="I6" s="64">
         <v>0.421603129334244</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -4905,19 +5273,19 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="56">
         <v>81133622000</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="58">
         <v>26954540000</v>
       </c>
-      <c r="G7" s="48">
+      <c r="G7" s="60">
         <v>54179082000</v>
       </c>
-      <c r="H7" s="50">
+      <c r="H7" s="62">
         <v>0.332224043935817</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7" s="64">
         <v>0.667775956064183</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -4932,47 +5300,47 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="55" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" s="45">
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="57">
         <v>1181271267000</v>
       </c>
-      <c r="F8" s="47">
+      <c r="F8" s="59">
         <v>614722181000</v>
       </c>
-      <c r="G8" s="49">
+      <c r="G8" s="61">
         <v>566549086000</v>
       </c>
-      <c r="H8" s="51">
+      <c r="H8" s="63">
         <v>0.520390360938154</v>
       </c>
-      <c r="I8" s="53">
+      <c r="I8" s="65">
         <v>0.479609639061846</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="J8" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4990,100 +5358,100 @@
   <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="78.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="15" max="16" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="79.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="15" max="16" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="67" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="67" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="67" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="67" t="inlineStr">
         <is>
           <t>IMCA total</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="67" t="inlineStr">
         <is>
           <t>IMCA adopción TIC</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="67" t="inlineStr">
         <is>
           <t>IMCA capacidades</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="67" t="inlineStr">
         <is>
           <t>IMCA dinamismo de los negocios</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="67" t="inlineStr">
         <is>
           <t>IMCA infraestructura</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="67" t="inlineStr">
         <is>
           <t>IMCA innovación</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="67" t="inlineStr">
         <is>
           <t>IMCA instituciones</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="67" t="inlineStr">
         <is>
           <t>IMCA mercado de bienes</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="67" t="inlineStr">
         <is>
           <t>IMCA mercado laboral</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="67" t="inlineStr">
         <is>
           <t>IMCA salud</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="67" t="inlineStr">
         <is>
           <t>IMCA sistema financiero</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="67" t="inlineStr">
         <is>
           <t>IMCA tamaño del mercado</t>
         </is>
@@ -5108,40 +5476,40 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="54">
+      <c r="E2" s="69">
         <v>31.3818515100941</v>
       </c>
-      <c r="F2" s="56">
+      <c r="F2" s="71">
         <v>2.63398487074733</v>
       </c>
-      <c r="G2" s="58">
+      <c r="G2" s="73">
         <v>38.0593025709489</v>
       </c>
-      <c r="H2" s="60">
+      <c r="H2" s="75">
         <v>60.3624944971642</v>
       </c>
-      <c r="I2" s="62">
+      <c r="I2" s="77">
         <v>43.9877153536879</v>
       </c>
-      <c r="J2" s="64">
+      <c r="J2" s="79">
         <v>0</v>
       </c>
-      <c r="K2" s="66">
+      <c r="K2" s="81">
         <v>46.1304222946339</v>
       </c>
-      <c r="L2" s="68">
+      <c r="L2" s="83">
         <v>3.97871320522783</v>
       </c>
-      <c r="M2" s="70">
+      <c r="M2" s="85">
         <v>58.3740276236263</v>
       </c>
-      <c r="N2" s="72">
+      <c r="N2" s="87">
         <v>56.8080765217646</v>
       </c>
-      <c r="O2" s="74">
+      <c r="O2" s="89">
         <v>13.260967027615</v>
       </c>
-      <c r="P2" s="76">
+      <c r="P2" s="91">
         <v>21.6046626456194</v>
       </c>
     </row>
@@ -5164,40 +5532,40 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="54">
+      <c r="E3" s="69">
         <v>32.2705141871298</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="71">
         <v>3.86947871943753</v>
       </c>
-      <c r="G3" s="58">
+      <c r="G3" s="73">
         <v>44.1148830157475</v>
       </c>
-      <c r="H3" s="60">
+      <c r="H3" s="75">
         <v>58.527947899254</v>
       </c>
-      <c r="I3" s="62">
+      <c r="I3" s="77">
         <v>41.556502631391</v>
       </c>
-      <c r="J3" s="64">
+      <c r="J3" s="79">
         <v>0</v>
       </c>
-      <c r="K3" s="66">
+      <c r="K3" s="81">
         <v>52.3745703335734</v>
       </c>
-      <c r="L3" s="68">
+      <c r="L3" s="83">
         <v>4.20365579477196</v>
       </c>
-      <c r="M3" s="70">
+      <c r="M3" s="85">
         <v>53.0234896711121</v>
       </c>
-      <c r="N3" s="72">
+      <c r="N3" s="87">
         <v>48.5132539013928</v>
       </c>
-      <c r="O3" s="74">
+      <c r="O3" s="89">
         <v>29.2556935794327</v>
       </c>
-      <c r="P3" s="76">
+      <c r="P3" s="91">
         <v>19.5361805123154</v>
       </c>
     </row>
@@ -5220,40 +5588,40 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="54">
+      <c r="E4" s="69">
         <v>29.3230806752124</v>
       </c>
-      <c r="F4" s="56">
+      <c r="F4" s="71">
         <v>7.27711172002022</v>
       </c>
-      <c r="G4" s="58">
+      <c r="G4" s="73">
         <v>32.4959236853539</v>
       </c>
-      <c r="H4" s="60">
+      <c r="H4" s="75">
         <v>60.3678210586547</v>
       </c>
-      <c r="I4" s="62">
+      <c r="I4" s="77">
         <v>32.9271282333142</v>
       </c>
-      <c r="J4" s="64">
+      <c r="J4" s="79">
         <v>0</v>
       </c>
-      <c r="K4" s="66">
+      <c r="K4" s="81">
         <v>42.1646532881667</v>
       </c>
-      <c r="L4" s="68">
+      <c r="L4" s="83">
         <v>3.6300755678387</v>
       </c>
-      <c r="M4" s="70">
+      <c r="M4" s="85">
         <v>68.3131031227284</v>
       </c>
-      <c r="N4" s="72">
+      <c r="N4" s="87">
         <v>25.5938441540071</v>
       </c>
-      <c r="O4" s="74">
+      <c r="O4" s="89">
         <v>33.5905985519738</v>
       </c>
-      <c r="P4" s="76">
+      <c r="P4" s="91">
         <v>16.1936280452786</v>
       </c>
     </row>
@@ -5276,40 +5644,40 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="54">
+      <c r="E5" s="69">
         <v>33.8874399946059</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="71">
         <v>10.2378557151926</v>
       </c>
-      <c r="G5" s="58">
+      <c r="G5" s="73">
         <v>41.4389481210448</v>
       </c>
-      <c r="H5" s="60">
+      <c r="H5" s="75">
         <v>59.6260932349973</v>
       </c>
-      <c r="I5" s="62">
+      <c r="I5" s="77">
         <v>49.248205980662</v>
       </c>
-      <c r="J5" s="64">
+      <c r="J5" s="79">
         <v>0</v>
       </c>
-      <c r="K5" s="66">
+      <c r="K5" s="81">
         <v>44.4672350389305</v>
       </c>
-      <c r="L5" s="68">
+      <c r="L5" s="83">
         <v>2.91875731066983</v>
       </c>
-      <c r="M5" s="70">
+      <c r="M5" s="85">
         <v>60.2229738904015</v>
       </c>
-      <c r="N5" s="72">
+      <c r="N5" s="87">
         <v>35.990779998679</v>
       </c>
-      <c r="O5" s="74">
+      <c r="O5" s="89">
         <v>47.0598944068256</v>
       </c>
-      <c r="P5" s="76">
+      <c r="P5" s="91">
         <v>21.5510962432616</v>
       </c>
     </row>
@@ -5332,40 +5700,40 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="69">
         <v>28.7268304657208</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="71">
         <v>3.1814365975342</v>
       </c>
-      <c r="G6" s="58">
+      <c r="G6" s="73">
         <v>34.9614396052838</v>
       </c>
-      <c r="H6" s="60">
+      <c r="H6" s="75">
         <v>49.7161934769108</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="77">
         <v>36.3789841028291</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="79">
         <v>0</v>
       </c>
-      <c r="K6" s="66">
+      <c r="K6" s="81">
         <v>56.1001179231328</v>
       </c>
-      <c r="L6" s="68">
+      <c r="L6" s="83">
         <v>3.32353793041221</v>
       </c>
-      <c r="M6" s="70">
+      <c r="M6" s="85">
         <v>57.6784173421928</v>
       </c>
-      <c r="N6" s="72">
+      <c r="N6" s="87">
         <v>41.434709703902</v>
       </c>
-      <c r="O6" s="74">
+      <c r="O6" s="89">
         <v>20.9433181178662</v>
       </c>
-      <c r="P6" s="76">
+      <c r="P6" s="91">
         <v>12.2769803228651</v>
       </c>
     </row>
@@ -5388,156 +5756,156 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="54">
+      <c r="E7" s="69">
         <v>27.2314013348499</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="71">
         <v>3.80325955090931</v>
       </c>
-      <c r="G7" s="58">
+      <c r="G7" s="73">
         <v>39.2988906887241</v>
       </c>
-      <c r="H7" s="60">
+      <c r="H7" s="75">
         <v>52.2697380065271</v>
       </c>
-      <c r="I7" s="62">
+      <c r="I7" s="77">
         <v>43.8773584548739</v>
       </c>
-      <c r="J7" s="64">
+      <c r="J7" s="79">
         <v>0</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="81">
         <v>42.4033881209276</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="83">
         <v>1.24268498748064</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="85">
         <v>40.0856613288448</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="87">
         <v>54.1176364815349</v>
       </c>
-      <c r="O7" s="74">
+      <c r="O7" s="89">
         <v>10.507320256107</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="91">
         <v>11.9394768074202</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="68" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE (por población 2022)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" s="55">
+      <c r="C8" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="70">
         <v>30.9608567890198</v>
       </c>
-      <c r="F8" s="57">
+      <c r="F8" s="72">
         <v>6.48185599227943</v>
       </c>
-      <c r="G8" s="59">
+      <c r="G8" s="74">
         <v>38.2872169287153</v>
       </c>
-      <c r="H8" s="61">
+      <c r="H8" s="76">
         <v>57.9491085895697</v>
       </c>
-      <c r="I8" s="63">
+      <c r="I8" s="78">
         <v>40.7639614637064</v>
       </c>
-      <c r="J8" s="65">
+      <c r="J8" s="80">
         <v>0</v>
       </c>
-      <c r="K8" s="67">
+      <c r="K8" s="82">
         <v>46.4667427907739</v>
       </c>
-      <c r="L8" s="69">
+      <c r="L8" s="84">
         <v>3.32123922277942</v>
       </c>
-      <c r="M8" s="71">
+      <c r="M8" s="86">
         <v>59.0861231949355</v>
       </c>
-      <c r="N8" s="73">
+      <c r="N8" s="88">
         <v>38.291429199359</v>
       </c>
-      <c r="O8" s="75">
+      <c r="O8" s="90">
         <v>32.2258327381697</v>
       </c>
-      <c r="P8" s="77">
+      <c r="P8" s="92">
         <v>17.6959145589298</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9" s="68" t="inlineStr">
         <is>
           <t>SUBREGIÓN OCCIDENTE (IMCA oficial de subregión)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="68" t="inlineStr">
         <is>
           <t>OCCIDENTE</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="55">
+      <c r="D9" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E9" s="70">
         <v>31.7778750125919</v>
       </c>
-      <c r="F9" s="57">
+      <c r="F9" s="72">
         <v>11.1355997417811</v>
       </c>
-      <c r="G9" s="59">
+      <c r="G9" s="74">
         <v>39.8497905507535</v>
       </c>
-      <c r="H9" s="61">
+      <c r="H9" s="76">
         <v>61.508126443671</v>
       </c>
-      <c r="I9" s="63">
+      <c r="I9" s="78">
         <v>44.8418590365667</v>
       </c>
-      <c r="J9" s="65">
+      <c r="J9" s="80">
         <v>0</v>
       </c>
-      <c r="K9" s="67">
+      <c r="K9" s="82">
         <v>49.9944215409497</v>
       </c>
-      <c r="L9" s="69">
+      <c r="L9" s="84">
         <v>6.97918002835241</v>
       </c>
-      <c r="M9" s="71">
+      <c r="M9" s="86">
         <v>46.8257087011245</v>
       </c>
-      <c r="N9" s="73">
+      <c r="N9" s="88">
         <v>45.1217806507044</v>
       </c>
-      <c r="O9" s="75">
+      <c r="O9" s="90">
         <v>25.2427616863391</v>
       </c>
-      <c r="P9" s="77">
+      <c r="P9" s="92">
         <v>18.0573967582682</v>
       </c>
     </row>
@@ -5553,101 +5921,101 @@
   <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="78.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="79.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="51.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="94" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="94" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="94" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="94" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="94" t="inlineStr">
         <is>
           <t>Índice de Gobierno Digital</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="94" t="inlineStr">
         <is>
           <t>Gobernanza</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="94" t="inlineStr">
         <is>
           <t>Innovación Pública Digital</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="94" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="94" t="inlineStr">
         <is>
           <t>Seguridad y Privacidad de la Información</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="94" t="inlineStr">
         <is>
           <t>Servicios Ciudadanos Digitales</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="94" t="inlineStr">
         <is>
           <t>Cultura y Apropiación</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="94" t="inlineStr">
         <is>
           <t>Servicios y Procesos Inteligentes</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="94" t="inlineStr">
         <is>
           <t>Estado Abierto</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="94" t="inlineStr">
         <is>
           <t>Decisiones basadas en datos</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="94" t="inlineStr">
         <is>
           <t>Proyectos de Transformación Digital</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="94" t="inlineStr">
         <is>
           <t>Estrategias de Ciudades y Territorios Inteligentes</t>
         </is>
@@ -5672,42 +6040,42 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="78">
+      <c r="E2" s="96">
         <v>35.28</v>
       </c>
-      <c r="F2" s="80">
+      <c r="F2" s="98">
         <v>33.33</v>
       </c>
-      <c r="G2" s="82">
+      <c r="G2" s="100">
         <v>0</v>
       </c>
-      <c r="H2" s="84">
+      <c r="H2" s="102">
         <v>0</v>
       </c>
-      <c r="I2" s="86">
+      <c r="I2" s="104">
         <v>25</v>
       </c>
-      <c r="J2" s="88">
+      <c r="J2" s="106">
         <v>0</v>
       </c>
-      <c r="K2" s="90">
+      <c r="K2" s="108">
         <v>0</v>
       </c>
-      <c r="L2" s="92">
+      <c r="L2" s="110">
         <v>0</v>
       </c>
-      <c r="M2" s="94">
+      <c r="M2" s="112">
         <v>47.22</v>
       </c>
-      <c r="N2" s="96">
+      <c r="N2" s="114">
         <v>0</v>
       </c>
-      <c r="O2" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" s="100" t="inlineStr">
+      <c r="O2" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5732,40 +6100,40 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="78">
+      <c r="E3" s="96">
         <v>63.46</v>
       </c>
-      <c r="F3" s="80">
+      <c r="F3" s="98">
         <v>100</v>
       </c>
-      <c r="G3" s="82">
+      <c r="G3" s="100">
         <v>75</v>
       </c>
-      <c r="H3" s="84">
+      <c r="H3" s="102">
         <v>41.11</v>
       </c>
-      <c r="I3" s="86">
+      <c r="I3" s="104">
         <v>52.54</v>
       </c>
-      <c r="J3" s="88">
+      <c r="J3" s="106">
         <v>75</v>
       </c>
-      <c r="K3" s="90">
+      <c r="K3" s="108">
         <v>60</v>
       </c>
-      <c r="L3" s="92">
+      <c r="L3" s="110">
         <v>11.11</v>
       </c>
-      <c r="M3" s="94">
+      <c r="M3" s="112">
         <v>86.59</v>
       </c>
-      <c r="N3" s="96">
+      <c r="N3" s="114">
         <v>27.59</v>
       </c>
-      <c r="O3" s="98">
+      <c r="O3" s="116">
         <v>100</v>
       </c>
-      <c r="P3" s="100" t="inlineStr">
+      <c r="P3" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5790,42 +6158,42 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="78">
+      <c r="E4" s="96">
         <v>66</v>
       </c>
-      <c r="F4" s="80">
+      <c r="F4" s="98">
         <v>62.56</v>
       </c>
-      <c r="G4" s="82">
+      <c r="G4" s="100">
         <v>0</v>
       </c>
-      <c r="H4" s="84">
+      <c r="H4" s="102">
         <v>22.22</v>
       </c>
-      <c r="I4" s="86">
+      <c r="I4" s="104">
         <v>79.46</v>
       </c>
-      <c r="J4" s="88">
+      <c r="J4" s="106">
         <v>20</v>
       </c>
-      <c r="K4" s="90">
+      <c r="K4" s="108">
         <v>97.14</v>
       </c>
-      <c r="L4" s="92">
+      <c r="L4" s="110">
         <v>0</v>
       </c>
-      <c r="M4" s="94">
+      <c r="M4" s="112">
         <v>76.83</v>
       </c>
-      <c r="N4" s="96">
+      <c r="N4" s="114">
         <v>75.86</v>
       </c>
-      <c r="O4" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" s="100" t="inlineStr">
+      <c r="O4" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5850,42 +6218,42 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="78">
+      <c r="E5" s="96">
         <v>51.58</v>
       </c>
-      <c r="F5" s="80">
+      <c r="F5" s="98">
         <v>63.83</v>
       </c>
-      <c r="G5" s="82">
+      <c r="G5" s="100">
         <v>0</v>
       </c>
-      <c r="H5" s="84">
+      <c r="H5" s="102">
         <v>16.67</v>
       </c>
-      <c r="I5" s="86">
+      <c r="I5" s="104">
         <v>27.27</v>
       </c>
-      <c r="J5" s="88">
+      <c r="J5" s="106">
         <v>0</v>
       </c>
-      <c r="K5" s="90">
+      <c r="K5" s="108">
         <v>56</v>
       </c>
-      <c r="L5" s="92">
+      <c r="L5" s="110">
         <v>0</v>
       </c>
-      <c r="M5" s="94">
+      <c r="M5" s="112">
         <v>65.33</v>
       </c>
-      <c r="N5" s="96">
+      <c r="N5" s="114">
         <v>40</v>
       </c>
-      <c r="O5" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" s="100" t="inlineStr">
+      <c r="O5" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5910,42 +6278,42 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="78">
+      <c r="E6" s="96">
         <v>16.02</v>
       </c>
-      <c r="F6" s="80">
+      <c r="F6" s="98">
         <v>41.75</v>
       </c>
-      <c r="G6" s="82">
+      <c r="G6" s="100">
         <v>0</v>
       </c>
-      <c r="H6" s="84">
+      <c r="H6" s="102">
         <v>16.67</v>
       </c>
-      <c r="I6" s="86">
+      <c r="I6" s="104">
         <v>25</v>
       </c>
-      <c r="J6" s="88">
+      <c r="J6" s="106">
         <v>0</v>
       </c>
-      <c r="K6" s="90">
+      <c r="K6" s="108">
         <v>0</v>
       </c>
-      <c r="L6" s="92">
+      <c r="L6" s="110">
         <v>0</v>
       </c>
-      <c r="M6" s="94">
+      <c r="M6" s="112">
         <v>18.67</v>
       </c>
-      <c r="N6" s="96">
+      <c r="N6" s="114">
         <v>10.34</v>
       </c>
-      <c r="O6" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" s="100" t="inlineStr">
+      <c r="O6" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5970,162 +6338,162 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="78">
+      <c r="E7" s="96">
         <v>11.04</v>
       </c>
-      <c r="F7" s="80">
+      <c r="F7" s="98">
         <v>41.58</v>
       </c>
-      <c r="G7" s="82">
+      <c r="G7" s="100">
         <v>0</v>
       </c>
-      <c r="H7" s="84">
+      <c r="H7" s="102">
         <v>0</v>
       </c>
-      <c r="I7" s="86">
+      <c r="I7" s="104">
         <v>25</v>
       </c>
-      <c r="J7" s="88">
+      <c r="J7" s="106">
         <v>0</v>
       </c>
-      <c r="K7" s="90">
+      <c r="K7" s="108">
         <v>72</v>
       </c>
-      <c r="L7" s="92">
+      <c r="L7" s="110">
         <v>0</v>
       </c>
-      <c r="M7" s="94">
+      <c r="M7" s="112">
         <v>6.94</v>
       </c>
-      <c r="N7" s="96">
+      <c r="N7" s="114">
         <v>0</v>
       </c>
-      <c r="O7" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P7" s="100" t="inlineStr">
+      <c r="O7" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="95" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE (por población 2024)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" s="79">
+      <c r="C8" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="97">
         <v>50.3561934393297</v>
       </c>
-      <c r="F8" s="81">
+      <c r="F8" s="99">
         <v>65.3129439721698</v>
       </c>
-      <c r="G8" s="83">
+      <c r="G8" s="101">
         <v>15.0398711384404</v>
       </c>
-      <c r="H8" s="85">
+      <c r="H8" s="103">
         <v>21.1735289938509</v>
       </c>
-      <c r="I8" s="87">
+      <c r="I8" s="105">
         <v>47.5328309120753</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="107">
         <v>21.0630466204464</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="109">
         <v>62.7301996619221</v>
       </c>
-      <c r="L8" s="93">
+      <c r="L8" s="111">
         <v>2.22790624464098</v>
       </c>
-      <c r="M8" s="95">
+      <c r="M8" s="113">
         <v>62.2781043141674</v>
       </c>
-      <c r="N8" s="97">
+      <c r="N8" s="115">
         <v>40.206139420368</v>
       </c>
-      <c r="O8" s="99">
+      <c r="O8" s="117">
         <v>100</v>
       </c>
-      <c r="P8" s="101" t="inlineStr">
+      <c r="P8" s="119" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9" s="95" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población 2024)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="95" t="inlineStr">
         <is>
           <t>OCCIDENTE</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="79">
+      <c r="D9" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E9" s="97">
         <v>56.2273877097285</v>
       </c>
-      <c r="F9" s="81">
+      <c r="F9" s="99">
         <v>68.8539535176784</v>
       </c>
-      <c r="G9" s="83">
+      <c r="G9" s="101">
         <v>26.9006294105998</v>
       </c>
-      <c r="H9" s="85">
+      <c r="H9" s="103">
         <v>26.4851025239433</v>
       </c>
-      <c r="I9" s="87">
+      <c r="I9" s="105">
         <v>50.4553803467272</v>
       </c>
-      <c r="J9" s="89">
+      <c r="J9" s="107">
         <v>36.7239335349608</v>
       </c>
-      <c r="K9" s="91">
+      <c r="K9" s="109">
         <v>58.8624628249442</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="111">
         <v>10.1003311550371</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="113">
         <v>69.1296690249874</v>
       </c>
-      <c r="N9" s="97">
+      <c r="N9" s="115">
         <v>42.6351604918269</v>
       </c>
-      <c r="O9" s="99">
+      <c r="O9" s="117">
         <v>81.6760874554875</v>
       </c>
-      <c r="P9" s="101">
+      <c r="P9" s="119">
         <v>81.0749459000825</v>
       </c>
     </row>
@@ -6141,35 +6509,35 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="54.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="55.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="51.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="121" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="121" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="121" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="121" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="121" t="inlineStr">
         <is>
           <t>Tasa de tránsito inmediato a la educación superior</t>
         </is>
@@ -6194,7 +6562,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="102">
+      <c r="E2" s="123">
         <v>0.526315789473684</v>
       </c>
     </row>
@@ -6217,7 +6585,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="102">
+      <c r="E3" s="123">
         <v>0.265193370165746</v>
       </c>
     </row>
@@ -6240,7 +6608,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="102">
+      <c r="E4" s="123">
         <v>0.378947368421053</v>
       </c>
     </row>
@@ -6263,7 +6631,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="102">
+      <c r="E5" s="123">
         <v>0.227272727272727</v>
       </c>
     </row>
@@ -6286,7 +6654,7 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="102">
+      <c r="E6" s="123">
         <v>0.65</v>
       </c>
     </row>
@@ -6309,32 +6677,32 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="102">
+      <c r="E7" s="123">
         <v>0.243243243243243</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="122" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" s="103">
+      <c r="C8" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="124">
         <v>0.381828749762742</v>
       </c>
     </row>
@@ -6350,53 +6718,53 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="54.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="49.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="58.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="94.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="59.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="126" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="126" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="126" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="126" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo por fibra óptica</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="126" t="inlineStr">
         <is>
           <t>Proporción de líneas sobre fibra óptica</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo por cada 1.000 habitantes</t>
         </is>
@@ -6421,17 +6789,17 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="104">
-        <v>792</v>
-      </c>
-      <c r="F2" s="106">
-        <v>556</v>
-      </c>
-      <c r="G2" s="108">
-        <v>0.702020202020202</v>
-      </c>
-      <c r="H2" s="110">
-        <v>282.151763448522</v>
+      <c r="E2" s="128">
+        <v>232</v>
+      </c>
+      <c r="F2" s="130">
+        <v>153</v>
+      </c>
+      <c r="G2" s="132">
+        <v>0.65948275862069</v>
+      </c>
+      <c r="H2" s="134">
+        <v>82.6505165657285</v>
       </c>
     </row>
     <row r="3">
@@ -6453,17 +6821,17 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="104">
-        <v>3668</v>
-      </c>
-      <c r="F3" s="106">
-        <v>2014</v>
-      </c>
-      <c r="G3" s="108">
-        <v>0.54907306434024</v>
-      </c>
-      <c r="H3" s="110">
-        <v>237.10407239819</v>
+      <c r="E3" s="128">
+        <v>1100</v>
+      </c>
+      <c r="F3" s="130">
+        <v>506</v>
+      </c>
+      <c r="G3" s="132">
+        <v>0.46</v>
+      </c>
+      <c r="H3" s="134">
+        <v>71.1053652230123</v>
       </c>
     </row>
     <row r="4">
@@ -6485,17 +6853,17 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="104">
-        <v>3974</v>
-      </c>
-      <c r="F4" s="106">
-        <v>2560</v>
-      </c>
-      <c r="G4" s="108">
-        <v>0.644187216909914</v>
-      </c>
-      <c r="H4" s="110">
-        <v>160.190261206063</v>
+      <c r="E4" s="128">
+        <v>1004</v>
+      </c>
+      <c r="F4" s="130">
+        <v>528</v>
+      </c>
+      <c r="G4" s="132">
+        <v>0.525896414342629</v>
+      </c>
+      <c r="H4" s="134">
+        <v>40.4708158658497</v>
       </c>
     </row>
     <row r="5">
@@ -6517,17 +6885,17 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="104">
-        <v>18505</v>
-      </c>
-      <c r="F5" s="106">
-        <v>16602</v>
-      </c>
-      <c r="G5" s="108">
-        <v>0.897162928938125</v>
-      </c>
-      <c r="H5" s="110">
-        <v>849.710717237579</v>
+      <c r="E5" s="128">
+        <v>4673</v>
+      </c>
+      <c r="F5" s="130">
+        <v>4129</v>
+      </c>
+      <c r="G5" s="132">
+        <v>0.883586561095656</v>
+      </c>
+      <c r="H5" s="134">
+        <v>214.574341078152</v>
       </c>
     </row>
     <row r="6">
@@ -6549,17 +6917,17 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="104">
-        <v>511</v>
-      </c>
-      <c r="F6" s="106">
-        <v>119</v>
-      </c>
-      <c r="G6" s="108">
-        <v>0.232876712328767</v>
-      </c>
-      <c r="H6" s="110">
-        <v>58.1872010931451</v>
+      <c r="E6" s="128">
+        <v>106</v>
+      </c>
+      <c r="F6" s="130">
+        <v>7</v>
+      </c>
+      <c r="G6" s="132">
+        <v>0.0660377358490566</v>
+      </c>
+      <c r="H6" s="134">
+        <v>12.0701434752904</v>
       </c>
     </row>
     <row r="7">
@@ -6581,51 +6949,51 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="104">
-        <v>1304</v>
-      </c>
-      <c r="F7" s="106">
-        <v>1040</v>
-      </c>
-      <c r="G7" s="108">
-        <v>0.797546012269939</v>
-      </c>
-      <c r="H7" s="110">
-        <v>174.916163648558</v>
+      <c r="E7" s="128">
+        <v>387</v>
+      </c>
+      <c r="F7" s="130">
+        <v>253</v>
+      </c>
+      <c r="G7" s="132">
+        <v>0.65374677002584</v>
+      </c>
+      <c r="H7" s="134">
+        <v>51.9114688128773</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO SIMPLE PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" s="105">
-        <v>4792.33333333333</v>
-      </c>
-      <c r="F8" s="107">
-        <v>3815.16666666667</v>
-      </c>
-      <c r="G8" s="109">
-        <v>0.637144356134531</v>
-      </c>
-      <c r="H8" s="111">
-        <v>293.710029838676</v>
+      <c r="A8" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="127" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE (suma de líneas; razones recalculadas sobre las sumas)</t>
+        </is>
+      </c>
+      <c r="C8" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="129">
+        <v>7502</v>
+      </c>
+      <c r="F8" s="131">
+        <v>5576</v>
+      </c>
+      <c r="G8" s="133">
+        <v>0.743268461743535</v>
+      </c>
+      <c r="H8" s="135">
+        <v>92.5030826140567</v>
       </c>
     </row>
   </sheetData>
